--- a/RAMON FRANCO/Junio/PRORRATEO-RAMON-FRANCO-JUNIO.xlsx
+++ b/RAMON FRANCO/Junio/PRORRATEO-RAMON-FRANCO-JUNIO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7928BEAE-2951-4420-8813-D08081EAA116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A0122B-C54F-4C66-BA7F-D6A03062D606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -277,7 +277,7 @@
     <t>GISELA</t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 16/06 LIQUIDACION : MAYO</t>
+    <t>EXPENSAS - VENCIMIENTO 14/07 LIQUIDACION: JUNIO</t>
   </si>
 </sst>
 </file>
@@ -673,7 +673,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -850,6 +850,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1309,7 +1310,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="25"/>
       <c r="C7" s="26">
-        <v>794642.4</v>
+        <v>1414065.58</v>
       </c>
       <c r="D7" s="26"/>
       <c r="F7" s="4"/>
@@ -1435,32 +1436,35 @@
         <v>7.99</v>
       </c>
       <c r="F12" s="58">
-        <v>183031.67816936001</v>
+        <v>261166.1401829088</v>
       </c>
       <c r="G12" s="44">
         <v>0</v>
       </c>
-      <c r="H12" s="69"/>
+      <c r="H12" s="88">
+        <f>F12</f>
+        <v>261166.1401829088</v>
+      </c>
       <c r="I12" s="44" t="e">
         <f>C9*E12/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J12" s="44">
         <f t="shared" ref="J12:J19" si="0">F12-G12-H12</f>
-        <v>183031.67816936001</v>
+        <v>0</v>
       </c>
       <c r="K12" s="44"/>
       <c r="L12" s="45">
         <f>(J12+K12)*8%</f>
-        <v>14642.534253548802</v>
+        <v>0</v>
       </c>
       <c r="M12" s="45">
         <f>J12+L12+K12</f>
-        <v>197674.21242290881</v>
+        <v>0</v>
       </c>
       <c r="N12" s="44">
         <f>C7*E12/100</f>
-        <v>63491.927760000006</v>
+        <v>112983.839842</v>
       </c>
       <c r="O12" s="44">
         <f t="shared" ref="O12:O29" si="1">C$10*E12/100</f>
@@ -1468,7 +1472,7 @@
       </c>
       <c r="P12" s="45">
         <f>N12+M12+O12</f>
-        <v>261166.1401829088</v>
+        <v>112983.839842</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1488,13 +1492,14 @@
         <v>6.05</v>
       </c>
       <c r="F13" s="58">
-        <v>181575.118202176</v>
+        <v>211506.99285835007</v>
       </c>
       <c r="G13" s="44">
         <v>0</v>
       </c>
-      <c r="H13" s="69">
-        <v>30250</v>
+      <c r="H13" s="88">
+        <f>F13</f>
+        <v>211506.99285835007</v>
       </c>
       <c r="I13" s="44" t="e">
         <f>C9*E13/100</f>
@@ -1502,20 +1507,20 @@
       </c>
       <c r="J13" s="44">
         <f>F13-G13-H13</f>
-        <v>151325.118202176</v>
+        <v>0</v>
       </c>
       <c r="K13" s="44"/>
       <c r="L13" s="45">
         <f t="shared" ref="L13:L29" si="2">(J13+K13)*8%</f>
-        <v>12106.009456174081</v>
+        <v>0</v>
       </c>
       <c r="M13" s="45">
         <f t="shared" ref="M13:M15" si="3">J13+L13+K13</f>
-        <v>163431.12765835007</v>
+        <v>0</v>
       </c>
       <c r="N13" s="44">
         <f>C7*E13/100</f>
-        <v>48075.865199999993</v>
+        <v>85550.96759</v>
       </c>
       <c r="O13" s="44">
         <f t="shared" si="1"/>
@@ -1523,7 +1528,7 @@
       </c>
       <c r="P13" s="45">
         <f t="shared" ref="P13:P29" si="4">N13+M13+O13</f>
-        <v>211506.99285835007</v>
+        <v>85550.96759</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1543,14 +1548,14 @@
         <v>6.02</v>
       </c>
       <c r="F14" s="58">
-        <v>77937.472479999997</v>
+        <v>47837.472479999997</v>
       </c>
       <c r="G14" s="44">
         <v>0</v>
       </c>
-      <c r="H14" s="69">
+      <c r="H14" s="88">
         <f t="shared" ref="H14:H29" si="5">F14</f>
-        <v>77937.472479999997</v>
+        <v>47837.472479999997</v>
       </c>
       <c r="I14" s="44" t="e">
         <f>C9*E14/100</f>
@@ -1571,7 +1576,7 @@
       </c>
       <c r="N14" s="44">
         <f>C7*E14/100</f>
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
       <c r="O14" s="44">
         <f t="shared" si="1"/>
@@ -1579,7 +1584,7 @@
       </c>
       <c r="P14" s="45">
         <f t="shared" si="4"/>
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1597,12 +1602,12 @@
         <v>7.63</v>
       </c>
       <c r="F15" s="60">
-        <v>98781.215120000008</v>
+        <v>60631.215120000001</v>
       </c>
       <c r="G15" s="46"/>
-      <c r="H15" s="69">
-        <f>F15</f>
-        <v>98781.215120000008</v>
+      <c r="H15" s="88">
+        <f t="shared" si="5"/>
+        <v>60631.215120000001</v>
       </c>
       <c r="I15" s="44" t="e">
         <f>C9*E15/100</f>
@@ -1623,7 +1628,7 @@
       </c>
       <c r="N15" s="50">
         <f>C7*E15/100</f>
-        <v>60631.215120000001</v>
+        <v>107893.20375400002</v>
       </c>
       <c r="O15" s="44">
         <f t="shared" si="1"/>
@@ -1631,7 +1636,7 @@
       </c>
       <c r="P15" s="45">
         <f t="shared" si="4"/>
-        <v>60631.215120000001</v>
+        <v>107893.20375400002</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1651,13 +1656,14 @@
         <v>6.05</v>
       </c>
       <c r="F16" s="58">
-        <v>121718.10519999999</v>
+        <v>146861.41881599999</v>
       </c>
       <c r="G16" s="46">
         <v>0</v>
       </c>
-      <c r="H16" s="69">
-        <v>30250</v>
+      <c r="H16" s="88">
+        <f>F16</f>
+        <v>146861.41881599999</v>
       </c>
       <c r="I16" s="44" t="e">
         <f>C9*E16/100</f>
@@ -1665,20 +1671,20 @@
       </c>
       <c r="J16" s="44">
         <f t="shared" si="0"/>
-        <v>91468.105199999991</v>
+        <v>0</v>
       </c>
       <c r="K16" s="44"/>
       <c r="L16" s="45">
         <f t="shared" si="2"/>
-        <v>7317.4484159999993</v>
+        <v>0</v>
       </c>
       <c r="M16" s="45">
         <f>J16+L16+K16</f>
-        <v>98785.55361599999</v>
+        <v>0</v>
       </c>
       <c r="N16" s="44">
         <f>C7*E16/100</f>
-        <v>48075.865199999993</v>
+        <v>85550.96759</v>
       </c>
       <c r="O16" s="44">
         <f t="shared" si="1"/>
@@ -1686,7 +1692,7 @@
       </c>
       <c r="P16" s="45">
         <f t="shared" si="4"/>
-        <v>146861.41881599999</v>
+        <v>85550.96759</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1706,14 +1712,14 @@
         <v>6.02</v>
       </c>
       <c r="F17" s="58">
-        <v>77937.472479999997</v>
+        <v>47837.472479999997</v>
       </c>
       <c r="G17" s="44">
         <v>0</v>
       </c>
-      <c r="H17" s="69">
+      <c r="H17" s="88">
         <f>F17</f>
-        <v>77937.472479999997</v>
+        <v>47837.472479999997</v>
       </c>
       <c r="I17" s="44" t="e">
         <f>C9*E17/100</f>
@@ -1734,7 +1740,7 @@
       </c>
       <c r="N17" s="44">
         <f>C7*E17/100</f>
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
       <c r="O17" s="44">
         <f t="shared" si="1"/>
@@ -1742,7 +1748,7 @@
       </c>
       <c r="P17" s="45">
         <f t="shared" si="4"/>
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1760,14 +1766,14 @@
         <v>7.63</v>
       </c>
       <c r="F18" s="58">
-        <v>98781.215120000008</v>
+        <v>60631.215120000001</v>
       </c>
       <c r="G18" s="44">
         <v>0</v>
       </c>
-      <c r="H18" s="69">
+      <c r="H18" s="88">
         <f t="shared" si="5"/>
-        <v>98781.215120000008</v>
+        <v>60631.215120000001</v>
       </c>
       <c r="I18" s="44" t="e">
         <f>C9*E18/100</f>
@@ -1788,7 +1794,7 @@
       </c>
       <c r="N18" s="44">
         <f>C7*E18/100</f>
-        <v>60631.215120000001</v>
+        <v>107893.20375400002</v>
       </c>
       <c r="O18" s="44">
         <f t="shared" si="1"/>
@@ -1796,7 +1802,7 @@
       </c>
       <c r="P18" s="45">
         <f t="shared" si="4"/>
-        <v>60631.215120000001</v>
+        <v>107893.20375400002</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1816,13 +1822,14 @@
         <v>6.05</v>
       </c>
       <c r="F19" s="58">
-        <v>177706.01531387659</v>
+        <v>188076.42732298671</v>
       </c>
       <c r="G19" s="44">
         <v>0</v>
       </c>
-      <c r="H19" s="69">
-        <v>48075.865199999993</v>
+      <c r="H19" s="88">
+        <f>F19</f>
+        <v>188076.42732298671</v>
       </c>
       <c r="I19" s="44" t="e">
         <f>C9*E19/100</f>
@@ -1830,20 +1837,20 @@
       </c>
       <c r="J19" s="44">
         <f t="shared" si="0"/>
-        <v>129630.15011387659</v>
+        <v>0</v>
       </c>
       <c r="K19" s="44"/>
       <c r="L19" s="45">
         <f t="shared" si="2"/>
-        <v>10370.412009110127</v>
+        <v>0</v>
       </c>
       <c r="M19" s="45">
         <f t="shared" si="6"/>
-        <v>140000.56212298671</v>
+        <v>0</v>
       </c>
       <c r="N19" s="44">
         <f>C7*E19/100</f>
-        <v>48075.865199999993</v>
+        <v>85550.96759</v>
       </c>
       <c r="O19" s="44">
         <f t="shared" si="1"/>
@@ -1851,7 +1858,7 @@
       </c>
       <c r="P19" s="45">
         <f>N19+M19+O19</f>
-        <v>188076.42732298671</v>
+        <v>85550.96759</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1869,14 +1876,14 @@
         <v>6.02</v>
       </c>
       <c r="F20" s="58">
-        <v>77937.472479999997</v>
+        <v>47837.472479999997</v>
       </c>
       <c r="G20" s="44">
         <v>0</v>
       </c>
-      <c r="H20" s="69">
+      <c r="H20" s="88">
         <f t="shared" si="5"/>
-        <v>77937.472479999997</v>
+        <v>47837.472479999997</v>
       </c>
       <c r="I20" s="44" t="e">
         <f>C9*E20/100</f>
@@ -1897,7 +1904,7 @@
       </c>
       <c r="N20" s="44">
         <f>C7*E20/100</f>
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
       <c r="O20" s="44">
         <f t="shared" si="1"/>
@@ -1905,7 +1912,7 @@
       </c>
       <c r="P20" s="45">
         <f t="shared" si="4"/>
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1923,14 +1930,14 @@
         <v>21.2</v>
       </c>
       <c r="F21" s="58">
-        <v>274464.1888</v>
+        <v>168464.1888</v>
       </c>
       <c r="G21" s="44">
         <v>0</v>
       </c>
-      <c r="H21" s="69">
+      <c r="H21" s="88">
         <f>F21</f>
-        <v>274464.1888</v>
+        <v>168464.1888</v>
       </c>
       <c r="I21" s="44" t="e">
         <f>C9*E21/100</f>
@@ -1951,7 +1958,7 @@
       </c>
       <c r="N21" s="44">
         <f>C7*E21/100</f>
-        <v>168464.1888</v>
+        <v>299781.90295999998</v>
       </c>
       <c r="O21" s="44">
         <f t="shared" si="1"/>
@@ -1959,7 +1966,7 @@
       </c>
       <c r="P21" s="45">
         <f t="shared" si="4"/>
-        <v>168464.1888</v>
+        <v>299781.90295999998</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1979,14 +1986,14 @@
         <v>6.81</v>
       </c>
       <c r="F22" s="58">
-        <v>88165.147440000001</v>
+        <v>54115.147440000001</v>
       </c>
       <c r="G22" s="44">
         <v>0</v>
       </c>
-      <c r="H22" s="69">
+      <c r="H22" s="88">
         <f>F22</f>
-        <v>88165.147440000001</v>
+        <v>54115.147440000001</v>
       </c>
       <c r="I22" s="44" t="e">
         <f>C9*E22/100</f>
@@ -2007,7 +2014,7 @@
       </c>
       <c r="N22" s="44">
         <f>C7*E22/100</f>
-        <v>54115.147440000001</v>
+        <v>96297.865997999994</v>
       </c>
       <c r="O22" s="44">
         <f t="shared" si="1"/>
@@ -2015,7 +2022,7 @@
       </c>
       <c r="P22" s="45">
         <f t="shared" si="4"/>
-        <v>54115.147440000001</v>
+        <v>96297.865997999994</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2035,33 +2042,34 @@
         <v>6.52</v>
       </c>
       <c r="F23" s="69">
-        <v>158652.84701587568</v>
+        <v>167199.87925714575</v>
       </c>
       <c r="G23" s="44">
         <v>0</v>
       </c>
-      <c r="H23" s="69">
-        <v>51811</v>
+      <c r="H23" s="88">
+        <f>F23</f>
+        <v>167199.87925714575</v>
       </c>
       <c r="I23" s="44">
         <v>0</v>
       </c>
       <c r="J23" s="44">
         <f t="shared" si="7"/>
-        <v>106841.84701587568</v>
+        <v>0</v>
       </c>
       <c r="K23" s="44"/>
       <c r="L23" s="67">
         <f t="shared" si="2"/>
-        <v>8547.3477612700553</v>
+        <v>0</v>
       </c>
       <c r="M23" s="67">
         <f>J23+L23+K23</f>
-        <v>115389.19477714573</v>
+        <v>0</v>
       </c>
       <c r="N23" s="44">
         <f>C7*E23/100</f>
-        <v>51810.684479999996</v>
+        <v>92197.075815999997</v>
       </c>
       <c r="O23" s="44">
         <f t="shared" si="1"/>
@@ -2069,7 +2077,7 @@
       </c>
       <c r="P23" s="45">
         <f t="shared" si="4"/>
-        <v>167199.87925714575</v>
+        <v>92197.075815999997</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2087,32 +2095,32 @@
         <v>1.18</v>
       </c>
       <c r="F24" s="58">
-        <v>386416.88855708716</v>
+        <v>426707.01996165415</v>
       </c>
       <c r="G24" s="44">
         <v>0</v>
       </c>
-      <c r="H24" s="69"/>
+      <c r="H24" s="88"/>
       <c r="I24" s="44" t="e">
         <f>C9*E24/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J24" s="44">
         <f t="shared" si="7"/>
-        <v>386416.88855708716</v>
+        <v>426707.01996165415</v>
       </c>
       <c r="K24" s="44"/>
       <c r="L24" s="45">
         <f t="shared" si="2"/>
-        <v>30913.351084566973</v>
+        <v>34136.561596932333</v>
       </c>
       <c r="M24" s="45">
         <f t="shared" si="6"/>
-        <v>417330.23964165413</v>
+        <v>460843.58155858651</v>
       </c>
       <c r="N24" s="44">
         <f>C7*E24/100</f>
-        <v>9376.7803199999998</v>
+        <v>16685.973844</v>
       </c>
       <c r="O24" s="44">
         <f t="shared" si="1"/>
@@ -2120,7 +2128,7 @@
       </c>
       <c r="P24" s="45">
         <f t="shared" si="4"/>
-        <v>426707.01996165415</v>
+        <v>477529.55540258653</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2138,12 +2146,12 @@
         <v>1.17</v>
       </c>
       <c r="F25" s="58">
-        <v>381293.02348021744</v>
+        <v>421093.78143863485</v>
       </c>
       <c r="G25" s="44">
         <v>0</v>
       </c>
-      <c r="H25" s="69">
+      <c r="H25" s="88">
         <v>0</v>
       </c>
       <c r="I25" s="44" t="e">
@@ -2152,20 +2160,20 @@
       </c>
       <c r="J25" s="44">
         <f t="shared" si="7"/>
-        <v>381293.02348021744</v>
+        <v>421093.78143863485</v>
       </c>
       <c r="K25" s="44"/>
       <c r="L25" s="45">
         <f t="shared" si="2"/>
-        <v>30503.441878417394</v>
+        <v>33687.50251509079</v>
       </c>
       <c r="M25" s="45">
         <f t="shared" si="6"/>
-        <v>411796.46535863483</v>
+        <v>454781.28395372565</v>
       </c>
       <c r="N25" s="44">
         <f>C7*E25/100</f>
-        <v>9297.3160800000005</v>
+        <v>16544.567286000001</v>
       </c>
       <c r="O25" s="44">
         <f t="shared" si="1"/>
@@ -2173,7 +2181,7 @@
       </c>
       <c r="P25" s="45">
         <f t="shared" si="4"/>
-        <v>421093.78143863485</v>
+        <v>471325.85123972566</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2191,14 +2199,14 @@
         <v>1.06</v>
       </c>
       <c r="F26" s="58">
-        <v>13723.209440000001</v>
+        <v>8423.2094400000005</v>
       </c>
       <c r="G26" s="44">
         <v>0</v>
       </c>
-      <c r="H26" s="69">
+      <c r="H26" s="88">
         <f>F26</f>
-        <v>13723.209440000001</v>
+        <v>8423.2094400000005</v>
       </c>
       <c r="I26" s="44" t="e">
         <f>C9*E26/100</f>
@@ -2219,7 +2227,7 @@
       </c>
       <c r="N26" s="44">
         <f>C7*E26/100</f>
-        <v>8423.2094400000005</v>
+        <v>14989.095148000002</v>
       </c>
       <c r="O26" s="44">
         <f t="shared" si="1"/>
@@ -2227,7 +2235,7 @@
       </c>
       <c r="P26" s="45">
         <f t="shared" si="4"/>
-        <v>8423.2094400000005</v>
+        <v>14989.095148000002</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2245,32 +2253,32 @@
         <v>0.51</v>
       </c>
       <c r="F27" s="58">
-        <v>19556.3002807753</v>
+        <v>25173.480543237325</v>
       </c>
       <c r="G27" s="44">
         <v>0</v>
       </c>
-      <c r="H27" s="69"/>
+      <c r="H27" s="88"/>
       <c r="I27" s="44" t="e">
         <f>C9*E27/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J27" s="44">
         <f t="shared" si="7"/>
-        <v>19556.3002807753</v>
+        <v>25173.480543237325</v>
       </c>
       <c r="K27" s="44"/>
       <c r="L27" s="45">
         <f t="shared" si="2"/>
-        <v>1564.5040224620241</v>
+        <v>2013.8784434589861</v>
       </c>
       <c r="M27" s="45">
         <f t="shared" si="6"/>
-        <v>21120.804303237324</v>
+        <v>27187.358986696312</v>
       </c>
       <c r="N27" s="44">
         <f>C7*E27/100</f>
-        <v>4052.6762400000002</v>
+        <v>7211.7344580000008</v>
       </c>
       <c r="O27" s="44">
         <f t="shared" si="1"/>
@@ -2278,7 +2286,7 @@
       </c>
       <c r="P27" s="45">
         <f t="shared" si="4"/>
-        <v>25173.480543237325</v>
+        <v>34399.093444696315</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2296,14 +2304,14 @@
         <v>0.27</v>
       </c>
       <c r="F28" s="58">
-        <v>3495.5344800000003</v>
+        <v>2145.5344800000003</v>
       </c>
       <c r="G28" s="44">
         <v>0</v>
       </c>
-      <c r="H28" s="69">
+      <c r="H28" s="88">
         <f t="shared" si="5"/>
-        <v>3495.5344800000003</v>
+        <v>2145.5344800000003</v>
       </c>
       <c r="I28" s="44" t="e">
         <f>C9*E28/100</f>
@@ -2324,7 +2332,7 @@
       </c>
       <c r="N28" s="44">
         <f>C7*E28/100</f>
-        <v>2145.5344800000003</v>
+        <v>3817.9770660000004</v>
       </c>
       <c r="O28" s="44">
         <f t="shared" si="1"/>
@@ -2332,7 +2340,7 @@
       </c>
       <c r="P28" s="45">
         <f t="shared" si="4"/>
-        <v>2145.5344800000003</v>
+        <v>3817.9770660000004</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2348,14 +2356,14 @@
         <v>1.82</v>
       </c>
       <c r="F29" s="59">
-        <v>23562.491679999999</v>
+        <v>14462.491680000001</v>
       </c>
       <c r="G29" s="44">
         <v>0</v>
       </c>
-      <c r="H29" s="69">
+      <c r="H29" s="88">
         <f t="shared" si="5"/>
-        <v>23562.491679999999</v>
+        <v>14462.491680000001</v>
       </c>
       <c r="I29" s="48"/>
       <c r="J29" s="44">
@@ -2373,7 +2381,7 @@
       </c>
       <c r="N29" s="48">
         <f>C7*E29/100</f>
-        <v>14462.491680000001</v>
+        <v>25735.993556000005</v>
       </c>
       <c r="O29" s="44">
         <f t="shared" si="1"/>
@@ -2381,7 +2389,7 @@
       </c>
       <c r="P29" s="45">
         <f t="shared" si="4"/>
-        <v>14462.491680000001</v>
+        <v>25735.993556000005</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
@@ -2394,7 +2402,7 @@
       <c r="E30" s="42"/>
       <c r="F30" s="54">
         <f>SUM(F12:F29)</f>
-        <v>2444735.3957393682</v>
+        <v>2360170.5599009171</v>
       </c>
       <c r="G30" s="54">
         <f>SUM(G12:G29)</f>
@@ -2402,22 +2410,22 @@
       </c>
       <c r="H30" s="62">
         <f>SUM(H12:H29)</f>
-        <v>995172.28472</v>
+        <v>1487196.277957391</v>
       </c>
       <c r="I30" s="54"/>
       <c r="J30" s="62">
         <f>SUM(J12:J29)</f>
-        <v>1449563.1110193683</v>
+        <v>872974.28194352624</v>
       </c>
       <c r="K30" s="54"/>
       <c r="L30" s="68">
         <f>L12+L13+L14+L15+L16+L17+L18+L19+L20+L21+L22+L23+L24+L25+L26+L27+L28+L29</f>
-        <v>115965.04888154946</v>
+        <v>69837.942555482121</v>
       </c>
       <c r="M30" s="55"/>
       <c r="N30" s="70">
         <f>SUM(N12:N29)</f>
-        <v>794642.4</v>
+        <v>1414065.5799999994</v>
       </c>
       <c r="O30" s="56">
         <f>SUM(O12:O29)</f>
@@ -2425,7 +2433,7 @@
       </c>
       <c r="P30" s="57">
         <f>SUM(P16:P29) +P15+P14+P13+P12</f>
-        <v>2360170.5599009176</v>
+        <v>2356877.8044990087</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
